--- a/tools/xlsform_samples/PAS.xlsx
+++ b/tools/xlsform_samples/PAS.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -796,84 +796,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PAS_scoring</t>
+          <t>PAS_proactive_attitude</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Computed Scores</t>
+          <t>proactive_attitude (mean_coded) - Mean of the administered language variant's items (reverse items recoded).</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>(${pas_en1} + ${pas_en2} + ${pas_en3} + ${pas_en4} + ${pas_en5} + ${pas_en6} + ${pas_en7} + ${pas_en8}) div 8</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PAS_proactive_attitude</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>proactive_attitude (mean_coded) - Mean of the administered language variant's items (reverse items recoded).</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>(${pas_en1} + ${pas_en2} + ${pas_en3} + ${pas_en4} + ${pas_en5} + ${pas_en6} + ${pas_en7} + ${pas_en8} + ${pas_de1} + ${pas_de2} + (5 - ${pas_de3}) + ${pas_de4} + (5 - ${pas_de5}) + ${pas_de6} + ${pas_de7} + (5 - ${pas_de8}) + ${pas_pb1} + (5 - ${pas_pb2}) + ${pas_pb3} + ${pas_pb4} + (5 - ${pas_pb5}) + ${pas_pb6} + ${pas_pb7} + (5 - ${pas_pb8}) + (5 - ${pas_pb9}) + ${pas_pb10} + (5 - ${pas_pb11}) + ${pas_pb12} + ${pas_pb13} + (5 - ${pas_pb14}) + ${pas_pb15}) div 31</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PAS_scoring</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tools/xlsform_samples/PAS.xlsx
+++ b/tools/xlsform_samples/PAS.xlsx
@@ -985,7 +985,11 @@
           <t>20260618</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>English (en)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
